--- a/data/SIC_Control Bienestar.xlsx
+++ b/data/SIC_Control Bienestar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alejandro.pastor\Documents\SIC\2026\Claude_SIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7BCBB7-4F3F-421E-8B93-404F9BB8D504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1B58E5-E20C-4DD5-8061-473BE373FF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2069" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="358">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1101,6 +1101,18 @@
   <si>
     <t>Hecho japi</t>
   </si>
+  <si>
+    <t>Cuello/Zona cervical, Cadera, Muslo</t>
+  </si>
+  <si>
+    <t>Cuello/Zona cervical, Brazo/Codo/Muneca/mano, Pierna</t>
+  </si>
+  <si>
+    <t>Cuello/Zona cervical, Zona Lumbar, Cadera</t>
+  </si>
+  <si>
+    <t>Cadera, Rodilla</t>
+  </si>
 </sst>
 </file>
 
@@ -1123,12 +1135,78 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE4A2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8A5C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBE3BD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE599"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6734D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5B87B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E3C6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5E4AB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0E4B5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFACF8A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E3CF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1143,21 +1221,54 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -34448,193 +34559,896 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1121" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1121" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1122" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1122" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1123" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1123" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1124" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1124" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1125" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1125" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1126" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1126" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1127" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1127" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1128" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1128" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1129" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1129" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1130" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1130" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1131" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1131" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1132" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1132" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1133" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1133" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1134" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1134" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1135" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1135" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1136" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1136" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1137" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1137" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1138" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1138" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1139" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1139" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1140" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1140" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1141" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1141" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1142" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1142" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1143" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1143" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1144" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1144" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1145" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1145" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1146" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1146" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1147" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1147" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1148" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1148" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1149" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1149" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1150" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="1121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1121" s="3">
+        <v>46265.389641203707</v>
+      </c>
+      <c r="B1121" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1121" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1121" s="5">
+        <v>2</v>
+      </c>
+      <c r="E1121" s="5">
+        <v>3</v>
+      </c>
+      <c r="F1121" s="5">
+        <v>2</v>
+      </c>
+      <c r="G1121" s="5">
+        <v>2</v>
+      </c>
+      <c r="H1121" s="4"/>
+      <c r="I1121" s="4"/>
+      <c r="J1121" s="4"/>
+      <c r="K1121" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1122" s="3">
+        <v>46265.389652777776</v>
+      </c>
+      <c r="B1122" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C1122" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1122" s="5">
+        <v>4</v>
+      </c>
+      <c r="E1122" s="5">
+        <v>3</v>
+      </c>
+      <c r="F1122" s="5">
+        <v>5</v>
+      </c>
+      <c r="G1122" s="5">
+        <v>3</v>
+      </c>
+      <c r="H1122" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1122" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1122" s="4"/>
+      <c r="K1122" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1123" s="3">
+        <v>46265.390057870369</v>
+      </c>
+      <c r="B1123" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1123" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1123" s="5">
+        <v>3</v>
+      </c>
+      <c r="E1123" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1123" s="5">
+        <v>1</v>
+      </c>
+      <c r="G1123" s="5">
+        <v>3</v>
+      </c>
+      <c r="H1123" s="4"/>
+      <c r="I1123" s="4"/>
+      <c r="J1123" s="4"/>
+      <c r="K1123" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1124" s="3">
+        <v>46265.390150462961</v>
+      </c>
+      <c r="B1124" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1124" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1124" s="5">
+        <v>3</v>
+      </c>
+      <c r="E1124" s="5">
+        <v>3</v>
+      </c>
+      <c r="F1124" s="5">
+        <v>3</v>
+      </c>
+      <c r="G1124" s="5">
+        <v>2</v>
+      </c>
+      <c r="H1124" s="4"/>
+      <c r="I1124" s="4"/>
+      <c r="J1124" s="4"/>
+      <c r="K1124" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1125" s="3">
+        <v>46265.392604166664</v>
+      </c>
+      <c r="B1125" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1125" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1125" s="5">
+        <v>5</v>
+      </c>
+      <c r="E1125" s="5">
+        <v>4</v>
+      </c>
+      <c r="F1125" s="5">
+        <v>4</v>
+      </c>
+      <c r="G1125" s="5">
+        <v>2</v>
+      </c>
+      <c r="H1125" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I1125" s="4"/>
+      <c r="J1125" s="4"/>
+      <c r="K1125" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1126" s="3">
+        <v>46265.392951388887</v>
+      </c>
+      <c r="B1126" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1126" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1126" s="5">
+        <v>2</v>
+      </c>
+      <c r="E1126" s="5">
+        <v>2</v>
+      </c>
+      <c r="F1126" s="5">
+        <v>4</v>
+      </c>
+      <c r="G1126" s="5">
+        <v>4</v>
+      </c>
+      <c r="H1126" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="I1126" s="4"/>
+      <c r="J1126" s="4"/>
+      <c r="K1126" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1127" s="3">
+        <v>46265.393136574072</v>
+      </c>
+      <c r="B1127" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1127" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1127" s="5">
+        <v>2</v>
+      </c>
+      <c r="E1127" s="5">
+        <v>4</v>
+      </c>
+      <c r="F1127" s="5">
+        <v>3</v>
+      </c>
+      <c r="G1127" s="5">
+        <v>3</v>
+      </c>
+      <c r="H1127" s="4"/>
+      <c r="I1127" s="4"/>
+      <c r="J1127" s="4"/>
+      <c r="K1127" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1128" s="3">
+        <v>46265.395648148151</v>
+      </c>
+      <c r="B1128" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1128" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1128" s="5">
+        <v>2</v>
+      </c>
+      <c r="E1128" s="5">
+        <v>3</v>
+      </c>
+      <c r="F1128" s="5">
+        <v>3</v>
+      </c>
+      <c r="G1128" s="5">
+        <v>2</v>
+      </c>
+      <c r="H1128" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1128" s="4"/>
+      <c r="J1128" s="4"/>
+      <c r="K1128" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1129" s="3">
+        <v>46265.396041666667</v>
+      </c>
+      <c r="B1129" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1129" s="5">
+        <v>5</v>
+      </c>
+      <c r="D1129" s="5">
+        <v>4</v>
+      </c>
+      <c r="E1129" s="5">
+        <v>2</v>
+      </c>
+      <c r="F1129" s="5">
+        <v>2</v>
+      </c>
+      <c r="G1129" s="5">
+        <v>4</v>
+      </c>
+      <c r="H1129" s="4"/>
+      <c r="I1129" s="4"/>
+      <c r="J1129" s="4"/>
+      <c r="K1129" s="12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1130" s="3">
+        <v>46265.396249999998</v>
+      </c>
+      <c r="B1130" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1130" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1130" s="5">
+        <v>2</v>
+      </c>
+      <c r="E1130" s="4"/>
+      <c r="F1130" s="5">
+        <v>3</v>
+      </c>
+      <c r="G1130" s="5">
+        <v>2</v>
+      </c>
+      <c r="H1130" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1130" s="4"/>
+      <c r="J1130" s="4"/>
+      <c r="K1130" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1131" s="3">
+        <v>46265.40047453704</v>
+      </c>
+      <c r="B1131" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1131" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1131" s="5">
+        <v>4</v>
+      </c>
+      <c r="E1131" s="5">
+        <v>3</v>
+      </c>
+      <c r="F1131" s="5">
+        <v>4</v>
+      </c>
+      <c r="G1131" s="5">
+        <v>2</v>
+      </c>
+      <c r="H1131" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1131" s="4"/>
+      <c r="J1131" s="4"/>
+      <c r="K1131" s="12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1132" s="3">
+        <v>46265.404293981483</v>
+      </c>
+      <c r="B1132" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1132" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1132" s="5">
+        <v>2</v>
+      </c>
+      <c r="E1132" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1132" s="5">
+        <v>2</v>
+      </c>
+      <c r="G1132" s="5">
+        <v>2</v>
+      </c>
+      <c r="H1132" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1132" s="4"/>
+      <c r="J1132" s="4"/>
+      <c r="K1132" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1133" s="3">
+        <v>46265.414467592593</v>
+      </c>
+      <c r="B1133" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1133" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1133" s="5">
+        <v>4</v>
+      </c>
+      <c r="E1133" s="5">
+        <v>2</v>
+      </c>
+      <c r="F1133" s="5">
+        <v>4</v>
+      </c>
+      <c r="G1133" s="5">
+        <v>3</v>
+      </c>
+      <c r="H1133" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1133" s="4"/>
+      <c r="J1133" s="4"/>
+      <c r="K1133" s="12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1134" s="3">
+        <v>46265.421840277777</v>
+      </c>
+      <c r="B1134" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1134" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1134" s="5">
+        <v>3</v>
+      </c>
+      <c r="E1134" s="5">
+        <v>3</v>
+      </c>
+      <c r="F1134" s="5">
+        <v>3</v>
+      </c>
+      <c r="G1134" s="5">
+        <v>3</v>
+      </c>
+      <c r="H1134" s="4"/>
+      <c r="I1134" s="4"/>
+      <c r="J1134" s="4"/>
+      <c r="K1134" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1135" s="3">
+        <v>46265.433553240742</v>
+      </c>
+      <c r="B1135" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1135" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1135" s="5">
+        <v>2</v>
+      </c>
+      <c r="E1135" s="5">
+        <v>2</v>
+      </c>
+      <c r="F1135" s="5">
+        <v>3</v>
+      </c>
+      <c r="G1135" s="5">
+        <v>3</v>
+      </c>
+      <c r="H1135" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="I1135" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1135" s="4"/>
+      <c r="K1135" s="14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1136" s="3">
+        <v>46265.4374537037</v>
+      </c>
+      <c r="B1136" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1136" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1136" s="5">
+        <v>2</v>
+      </c>
+      <c r="E1136" s="5">
+        <v>2</v>
+      </c>
+      <c r="F1136" s="5">
+        <v>2</v>
+      </c>
+      <c r="G1136" s="5">
+        <v>2</v>
+      </c>
+      <c r="H1136" s="4"/>
+      <c r="I1136" s="4"/>
+      <c r="J1136" s="4"/>
+      <c r="K1136" s="15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1137" s="3">
+        <v>46265.454189814816</v>
+      </c>
+      <c r="B1137" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1137" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1137" s="5">
+        <v>4</v>
+      </c>
+      <c r="E1137" s="5">
+        <v>3</v>
+      </c>
+      <c r="F1137" s="5">
+        <v>4</v>
+      </c>
+      <c r="G1137" s="5">
+        <v>2</v>
+      </c>
+      <c r="H1137" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1137" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J1137" s="4"/>
+      <c r="K1137" s="16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1138" s="3">
+        <v>46265.483206018522</v>
+      </c>
+      <c r="B1138" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1138" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1138" s="5">
+        <v>3</v>
+      </c>
+      <c r="E1138" s="5">
+        <v>2</v>
+      </c>
+      <c r="F1138" s="5">
+        <v>4</v>
+      </c>
+      <c r="G1138" s="5">
+        <v>3</v>
+      </c>
+      <c r="H1138" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="I1138" s="4"/>
+      <c r="J1138" s="4"/>
+      <c r="K1138" s="16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1139" s="3">
+        <v>46265.491562499999</v>
+      </c>
+      <c r="B1139" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1139" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1139" s="5">
+        <v>3</v>
+      </c>
+      <c r="E1139" s="5">
+        <v>2</v>
+      </c>
+      <c r="F1139" s="5">
+        <v>4</v>
+      </c>
+      <c r="G1139" s="5">
+        <v>3</v>
+      </c>
+      <c r="H1139" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I1139" s="4"/>
+      <c r="J1139" s="4"/>
+      <c r="K1139" s="16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1140" s="3">
+        <v>46265.510231481479</v>
+      </c>
+      <c r="B1140" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1140" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1140" s="5">
+        <v>3</v>
+      </c>
+      <c r="E1140" s="5">
+        <v>2</v>
+      </c>
+      <c r="F1140" s="5">
+        <v>2</v>
+      </c>
+      <c r="G1140" s="5">
+        <v>2</v>
+      </c>
+      <c r="H1140" s="4"/>
+      <c r="I1140" s="4"/>
+      <c r="J1140" s="4"/>
+      <c r="K1140" s="14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1141" s="3">
+        <v>46265.700775462959</v>
+      </c>
+      <c r="B1141" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1141" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1141" s="5">
+        <v>1</v>
+      </c>
+      <c r="E1141" s="5">
+        <v>3</v>
+      </c>
+      <c r="F1141" s="5">
+        <v>1</v>
+      </c>
+      <c r="G1141" s="5">
+        <v>1</v>
+      </c>
+      <c r="H1141" s="4"/>
+      <c r="I1141" s="4"/>
+      <c r="J1141" s="4"/>
+      <c r="K1141" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1142" s="3">
+        <v>46265.700995370367</v>
+      </c>
+      <c r="B1142" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1142" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1142" s="5">
+        <v>2</v>
+      </c>
+      <c r="E1142" s="5">
+        <v>2</v>
+      </c>
+      <c r="F1142" s="5">
+        <v>3</v>
+      </c>
+      <c r="G1142" s="5">
+        <v>3</v>
+      </c>
+      <c r="H1142" s="4"/>
+      <c r="I1142" s="4"/>
+      <c r="J1142" s="4"/>
+      <c r="K1142" s="14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1143" s="3">
+        <v>46265.70108796296</v>
+      </c>
+      <c r="B1143" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1143" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1143" s="5">
+        <v>2</v>
+      </c>
+      <c r="E1143" s="5">
+        <v>3</v>
+      </c>
+      <c r="F1143" s="5">
+        <v>3</v>
+      </c>
+      <c r="G1143" s="5">
+        <v>3</v>
+      </c>
+      <c r="H1143" s="4"/>
+      <c r="I1143" s="4"/>
+      <c r="J1143" s="4"/>
+      <c r="K1143" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1144" s="3">
+        <v>46265.701157407406</v>
+      </c>
+      <c r="B1144" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1144" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1144" s="5">
+        <v>4</v>
+      </c>
+      <c r="E1144" s="5">
+        <v>4</v>
+      </c>
+      <c r="F1144" s="5">
+        <v>2</v>
+      </c>
+      <c r="G1144" s="5">
+        <v>3</v>
+      </c>
+      <c r="H1144" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1144" s="4"/>
+      <c r="J1144" s="4"/>
+      <c r="K1144" s="16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1145" s="3">
+        <v>46265.701249999998</v>
+      </c>
+      <c r="B1145" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1145" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1145" s="5">
+        <v>4</v>
+      </c>
+      <c r="E1145" s="5">
+        <v>3</v>
+      </c>
+      <c r="F1145" s="5">
+        <v>4</v>
+      </c>
+      <c r="G1145" s="5">
+        <v>4</v>
+      </c>
+      <c r="H1145" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="I1145" s="4"/>
+      <c r="J1145" s="4"/>
+      <c r="K1145" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1146" s="3">
+        <v>46265.701273148145</v>
+      </c>
+      <c r="B1146" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1146" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1146" s="5">
+        <v>1</v>
+      </c>
+      <c r="E1146" s="5">
+        <v>2</v>
+      </c>
+      <c r="F1146" s="5">
+        <v>1</v>
+      </c>
+      <c r="G1146" s="5">
+        <v>3</v>
+      </c>
+      <c r="H1146" s="4"/>
+      <c r="I1146" s="4"/>
+      <c r="J1146" s="4"/>
+      <c r="K1146" s="17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1147" s="3">
+        <v>46265.70140046296</v>
+      </c>
+      <c r="B1147" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1147" s="5">
+        <v>4</v>
+      </c>
+      <c r="D1147" s="5">
+        <v>2</v>
+      </c>
+      <c r="E1147" s="5">
+        <v>3</v>
+      </c>
+      <c r="F1147" s="5">
+        <v>3</v>
+      </c>
+      <c r="G1147" s="5">
+        <v>3</v>
+      </c>
+      <c r="H1147" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="I1147" s="4"/>
+      <c r="J1147" s="4"/>
+      <c r="K1147" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1148" s="3">
+        <v>46265.702233796299</v>
+      </c>
+      <c r="B1148" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1148" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1148" s="5">
+        <v>2</v>
+      </c>
+      <c r="E1148" s="5">
+        <v>3</v>
+      </c>
+      <c r="F1148" s="5">
+        <v>3</v>
+      </c>
+      <c r="G1148" s="5">
+        <v>2</v>
+      </c>
+      <c r="H1148" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1148" s="4"/>
+      <c r="J1148" s="4"/>
+      <c r="K1148" s="14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1149" s="3">
+        <v>46265.708622685182</v>
+      </c>
+      <c r="B1149" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1149" s="5">
+        <v>3</v>
+      </c>
+      <c r="D1149" s="5">
+        <v>3</v>
+      </c>
+      <c r="E1149" s="5">
+        <v>3</v>
+      </c>
+      <c r="F1149" s="5">
+        <v>3</v>
+      </c>
+      <c r="G1149" s="5">
+        <v>3</v>
+      </c>
+      <c r="H1149" s="4"/>
+      <c r="I1149" s="4"/>
+      <c r="J1149" s="4"/>
+      <c r="K1149" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="K1150" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="1151" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="1151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="K1151" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="1152" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="1152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="K1152" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -35404,7 +36218,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L1278" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="K2:K1066 K1121:K2166">
+  <conditionalFormatting sqref="K2:K1066 K1150:K2166">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="formula" val="5"/>
@@ -35417,7 +36231,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:G1066 C1121:G2166" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:G1066 C1150:G2166" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"5,4,3,2,1"</formula1>
     </dataValidation>
   </dataValidations>
